--- a/artfynd/A 42634-2025 artfynd.xlsx
+++ b/artfynd/A 42634-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>111258263</v>
       </c>
       <c r="B2" t="n">
-        <v>90151</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -726,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>523456.9952807766</v>
+        <v>523457</v>
       </c>
       <c r="R2" t="n">
-        <v>6619607.904217144</v>
+        <v>6619608</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,19 +754,9 @@
           <t>2023-08-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-08-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,15 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111258411</v>
+        <v>111258364</v>
       </c>
       <c r="B3" t="n">
-        <v>90151</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -834,7 +814,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -850,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523470.5156865339</v>
+        <v>523499</v>
       </c>
       <c r="R3" t="n">
-        <v>6619547.445112181</v>
+        <v>6619594</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,19 +863,9 @@
           <t>2023-08-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-08-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,15 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111661270</v>
+        <v>111258411</v>
       </c>
       <c r="B4" t="n">
-        <v>57181</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -939,49 +904,48 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100067</v>
+        <v>366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>6K+</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bornsviken, Vstm</t>
+          <t>Bornsviken, Ramsbergs sn, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523467</v>
+        <v>523471</v>
       </c>
       <c r="R4" t="n">
-        <v>6619465</v>
+        <v>6619547</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1005,12 +969,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-07-27</t>
+          <t>2023-08-03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-07-27</t>
+          <t>2023-08-03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,6 +983,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1037,56 +1002,59 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111660401</v>
+        <v>111258443</v>
       </c>
       <c r="B5" t="n">
-        <v>90666</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bornsviken, Vstm</t>
+          <t>Bornsviken, Ramsbergs sn, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>523379</v>
+        <v>523494</v>
       </c>
       <c r="R5" t="n">
-        <v>6619784</v>
+        <v>6619507</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1110,17 +1078,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-08-23</t>
+          <t>2023-08-03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-08-23</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>gamla kroppar, en ny på gång</t>
+          <t>2023-08-03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,42 +1111,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111940619</v>
+        <v>112280663</v>
       </c>
       <c r="B6" t="n">
-        <v>90837</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91394</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>2051</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1199,10 +1157,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>523436</v>
+        <v>523468</v>
       </c>
       <c r="R6" t="n">
-        <v>6619488</v>
+        <v>6619512</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1262,15 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112299318</v>
+        <v>111660362</v>
       </c>
       <c r="B7" t="n">
-        <v>90898</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,21 +1231,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5448</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1305,10 +1258,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>523421</v>
+        <v>523381</v>
       </c>
       <c r="R7" t="n">
-        <v>6619764</v>
+        <v>6619759</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1335,12 +1288,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-09-22</t>
+          <t>2022-08-20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-09-22</t>
+          <t>2022-08-20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1368,15 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112280554</v>
+        <v>111660401</v>
       </c>
       <c r="B8" t="n">
-        <v>90878</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1384,21 +1332,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1411,10 +1359,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>523456</v>
+        <v>523379</v>
       </c>
       <c r="R8" t="n">
-        <v>6619581</v>
+        <v>6619784</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1441,12 +1389,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2023-08-23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2023-08-23</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>gamla kroppar, en ny på gång</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,15 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112279547</v>
+        <v>111940654</v>
       </c>
       <c r="B9" t="n">
-        <v>90878</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1490,25 +1438,33 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5966</v>
+        <v>4366</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
@@ -1517,10 +1473,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>523438</v>
+        <v>523487</v>
       </c>
       <c r="R9" t="n">
-        <v>6619852</v>
+        <v>6619508</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1547,12 +1503,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-09-06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-09-06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1580,37 +1536,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112299293</v>
+        <v>111657844</v>
       </c>
       <c r="B10" t="n">
-        <v>90878</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89106</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5966</v>
+        <v>4394</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Honungsvaxing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hygrocybe reidii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Kühner</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1623,10 +1574,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>523388</v>
+        <v>523495</v>
       </c>
       <c r="R10" t="n">
-        <v>6619773</v>
+        <v>6619514</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1653,12 +1604,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-09-22</t>
+          <t>2023-08-23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-09-22</t>
+          <t>2023-08-23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1686,41 +1637,44 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112300026</v>
+        <v>112279929</v>
       </c>
       <c r="B11" t="n">
-        <v>89103</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89138</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2051</v>
+        <v>4404</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Sotvaxskivling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Hygrophorus camarophyllus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Dumée &amp; al.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1729,10 +1683,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>523468</v>
+        <v>523385</v>
       </c>
       <c r="R11" t="n">
-        <v>6619512</v>
+        <v>6619779</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1759,12 +1713,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
+          <t>2023-09-22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
+          <t>2023-09-22</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1792,43 +1746,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112280610</v>
+        <v>112280232</v>
       </c>
       <c r="B12" t="n">
-        <v>95751</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89138</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221946</v>
+        <v>4404</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Sotvaxskivling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Hygrophorus camarophyllus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Dumée &amp; al.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1836,10 +1784,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>523437</v>
+        <v>523440</v>
       </c>
       <c r="R12" t="n">
-        <v>6619563</v>
+        <v>6619756</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1899,15 +1847,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112792164</v>
+        <v>112280476</v>
       </c>
       <c r="B13" t="n">
-        <v>91222</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89138</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1915,21 +1858,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5966</v>
+        <v>4404</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Sotvaxskivling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hygrophorus camarophyllus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Alb. &amp; Schwein.) Dumée &amp; al.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1942,10 +1885,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>523437</v>
+        <v>523483</v>
       </c>
       <c r="R13" t="n">
-        <v>6619842</v>
+        <v>6619644</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1972,12 +1915,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-09-22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-09-22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2005,15 +1948,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112792120</v>
+        <v>112792184</v>
       </c>
       <c r="B14" t="n">
-        <v>91222</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89138</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2021,26 +1959,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5966</v>
+        <v>4404</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Sotvaxskivling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hygrophorus camarophyllus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Alb. &amp; Schwein.) Dumée &amp; al.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2056,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>523418</v>
+        <v>523470</v>
       </c>
       <c r="R14" t="n">
-        <v>6619830</v>
+        <v>6619801</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2116,6 +2054,1892 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>111259031</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91893</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4660</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Rävticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Inocutis rheades</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bornsviken, Ramsbergs sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>523491</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6619617</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-08-03</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-08-03</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>gamla kroppar</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>111350555</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>523346</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6619799</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2023-08-03</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2023-08-03</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>112280158</v>
+      </c>
+      <c r="B17" t="n">
+        <v>93223</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>523421</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6619764</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>111940426</v>
+      </c>
+      <c r="B18" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>523334</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6619818</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>112280122</v>
+      </c>
+      <c r="B19" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>523356</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6619775</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>111940619</v>
+      </c>
+      <c r="B20" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>523436</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6619488</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>112279547</v>
+      </c>
+      <c r="B21" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>523438</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6619852</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>112280064</v>
+      </c>
+      <c r="B22" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>523388</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6619773</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>112280554</v>
+      </c>
+      <c r="B23" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>523456</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6619581</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2023-09-23</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2023-09-23</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>112299136</v>
+      </c>
+      <c r="B24" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>523459</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6619798</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>112299188</v>
+      </c>
+      <c r="B25" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>523355</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6619797</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>112792120</v>
+      </c>
+      <c r="B26" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>523418</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6619830</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>112792164</v>
+      </c>
+      <c r="B27" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>523437</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6619842</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>112792096</v>
+      </c>
+      <c r="B28" t="n">
+        <v>92567</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>523489</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6619760</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>111661270</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100067</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Havsörn</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Haliaeetus albicilla</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>6K+</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>523467</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6619465</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>121150984</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Morskoga, Vstm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>523349</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6619695</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>111660445</v>
+      </c>
+      <c r="B31" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>523338</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6619822</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2023-08-03</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2023-08-03</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>112280610</v>
+      </c>
+      <c r="B32" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>523437</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6619563</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42634-2025 artfynd.xlsx
+++ b/artfynd/A 42634-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AZ32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111258263</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111258364</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -999,6 +1014,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111258411</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1108,6 +1128,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111258443</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1217,6 +1242,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112280663</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1318,6 +1348,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111660362</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1424,6 +1459,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111660401</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1533,6 +1573,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111940654</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1634,6 +1679,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111657844</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1743,6 +1793,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112279929</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1844,6 +1899,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112280232</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1945,6 +2005,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112280476</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2054,6 +2119,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112792184</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2168,6 +2238,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111259031</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2277,6 +2352,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111350555</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2378,6 +2458,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112280158</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2487,6 +2572,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111940426</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2588,6 +2678,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112280122</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2697,6 +2792,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111940619</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2798,6 +2898,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112279547</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2899,6 +3004,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112280064</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3000,6 +3110,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112280554</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3109,6 +3224,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112299136</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3210,6 +3330,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112299188</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3319,6 +3444,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112792120</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3420,6 +3550,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112792164</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3521,6 +3656,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112792096</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3630,6 +3770,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111661270</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3736,6 +3881,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121150984</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3838,6 +3988,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111660445</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3940,8 +4095,46 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112280610</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>